--- a/output/yearly_total_coral_cover_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_93_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.257418959880396</v>
+        <v>1.251145592050259</v>
       </c>
       <c r="C3" t="n">
-        <v>4.634474428392712</v>
+        <v>4.598984248884189</v>
       </c>
       <c r="D3" t="n">
-        <v>6.04874895807861</v>
+        <v>6.076728767649644</v>
       </c>
       <c r="E3" t="n">
-        <v>11.94064234635172</v>
+        <v>11.92685860858409</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.379903358837938</v>
+        <v>1.37393670371728</v>
       </c>
       <c r="C4" t="n">
-        <v>5.138627089422211</v>
+        <v>5.047278060534623</v>
       </c>
       <c r="D4" t="n">
-        <v>6.347279921051703</v>
+        <v>6.264636678240109</v>
       </c>
       <c r="E4" t="n">
-        <v>12.86581036931185</v>
+        <v>12.68585144249201</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.55219036576013</v>
+        <v>1.542341257631959</v>
       </c>
       <c r="C5" t="n">
-        <v>5.757873869974589</v>
+        <v>5.594472545213489</v>
       </c>
       <c r="D5" t="n">
-        <v>6.681208690602809</v>
+        <v>6.567265043255849</v>
       </c>
       <c r="E5" t="n">
-        <v>13.99127292633753</v>
+        <v>13.7040788461013</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.744255949767872</v>
+        <v>1.747612221622471</v>
       </c>
       <c r="C6" t="n">
-        <v>6.495531031564788</v>
+        <v>6.242349971300674</v>
       </c>
       <c r="D6" t="n">
-        <v>7.057204382765399</v>
+        <v>6.948573607702313</v>
       </c>
       <c r="E6" t="n">
-        <v>15.29699136409806</v>
+        <v>14.93853580062546</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.970783101766041</v>
+        <v>1.982004758522603</v>
       </c>
       <c r="C7" t="n">
-        <v>7.367423550713587</v>
+        <v>6.998969857232018</v>
       </c>
       <c r="D7" t="n">
-        <v>7.405327863718052</v>
+        <v>7.371868606316609</v>
       </c>
       <c r="E7" t="n">
-        <v>16.74353451619768</v>
+        <v>16.35284322207123</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.208207891756508</v>
+        <v>1.226615879485393</v>
       </c>
       <c r="C8" t="n">
-        <v>5.010232085199126</v>
+        <v>4.641841978649753</v>
       </c>
       <c r="D8" t="n">
-        <v>5.743766818878751</v>
+        <v>5.616203594633136</v>
       </c>
       <c r="E8" t="n">
-        <v>11.96220679583439</v>
+        <v>11.48466145276828</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.508787366344034</v>
+        <v>1.557469885837648</v>
       </c>
       <c r="C9" t="n">
-        <v>6.139770362827706</v>
+        <v>5.659737826918178</v>
       </c>
       <c r="D9" t="n">
-        <v>6.293774357019844</v>
+        <v>6.110589224554074</v>
       </c>
       <c r="E9" t="n">
-        <v>13.94233208619158</v>
+        <v>13.3277969373099</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.824289896144001</v>
+        <v>1.911720116960858</v>
       </c>
       <c r="C10" t="n">
-        <v>7.433194146844643</v>
+        <v>6.824736639878211</v>
       </c>
       <c r="D10" t="n">
-        <v>6.834148430915475</v>
+        <v>6.660718469236911</v>
       </c>
       <c r="E10" t="n">
-        <v>16.09163247390412</v>
+        <v>15.39717522607598</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.138051465660778</v>
+        <v>2.285999411858154</v>
       </c>
       <c r="C11" t="n">
-        <v>8.886047749280554</v>
+        <v>8.10607334096418</v>
       </c>
       <c r="D11" t="n">
-        <v>7.317309504034418</v>
+        <v>7.303802725241177</v>
       </c>
       <c r="E11" t="n">
-        <v>18.34140871897575</v>
+        <v>17.69587547806351</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.47247850664315</v>
+        <v>2.661941224267887</v>
       </c>
       <c r="C12" t="n">
-        <v>10.46717513704579</v>
+        <v>9.471984570411204</v>
       </c>
       <c r="D12" t="n">
-        <v>7.771941796911083</v>
+        <v>7.830067568076478</v>
       </c>
       <c r="E12" t="n">
-        <v>20.71159544060002</v>
+        <v>19.96399336275557</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.798729352445054</v>
+        <v>3.029526068388456</v>
       </c>
       <c r="C13" t="n">
-        <v>12.10203512268866</v>
+        <v>10.87744797934758</v>
       </c>
       <c r="D13" t="n">
-        <v>8.254979601017915</v>
+        <v>8.426876708686668</v>
       </c>
       <c r="E13" t="n">
-        <v>23.15574407615163</v>
+        <v>22.33385075642271</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.624419386400857</v>
+        <v>1.745851759939145</v>
       </c>
       <c r="C14" t="n">
-        <v>8.532712909305516</v>
+        <v>7.648168045256182</v>
       </c>
       <c r="D14" t="n">
-        <v>6.254714623756429</v>
+        <v>6.450298401396479</v>
       </c>
       <c r="E14" t="n">
-        <v>16.4118469194628</v>
+        <v>15.84431820659181</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.666241838601772</v>
+        <v>1.798993763170025</v>
       </c>
       <c r="C15" t="n">
-        <v>9.294156428719342</v>
+        <v>8.198094021790034</v>
       </c>
       <c r="D15" t="n">
-        <v>6.261037078971778</v>
+        <v>6.528671320626502</v>
       </c>
       <c r="E15" t="n">
-        <v>17.22143534629289</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.940169083040717</v>
+        <v>2.123490831854723</v>
       </c>
       <c r="C16" t="n">
-        <v>11.04518199905987</v>
+        <v>9.675084355444147</v>
       </c>
       <c r="D16" t="n">
-        <v>6.714683058150144</v>
+        <v>7.061721054124349</v>
       </c>
       <c r="E16" t="n">
-        <v>19.70003414025073</v>
+        <v>18.86029624142322</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.563217234518112</v>
+        <v>1.727944681813684</v>
       </c>
       <c r="C17" t="n">
-        <v>10.24668732128777</v>
+        <v>8.9639161359648</v>
       </c>
       <c r="D17" t="n">
-        <v>6.213343775499469</v>
+        <v>6.615114205985433</v>
       </c>
       <c r="E17" t="n">
-        <v>18.02324833130535</v>
+        <v>17.30697502376392</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.78747786259921</v>
+        <v>2.001940648591926</v>
       </c>
       <c r="C18" t="n">
-        <v>12.02998293866689</v>
+        <v>10.46276999099249</v>
       </c>
       <c r="D18" t="n">
-        <v>6.583943716375597</v>
+        <v>7.088277329524225</v>
       </c>
       <c r="E18" t="n">
-        <v>20.40140451764169</v>
+        <v>19.55298796910864</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.793230904146097</v>
+        <v>2.035752039526186</v>
       </c>
       <c r="C19" t="n">
-        <v>12.95295340786044</v>
+        <v>11.19739216312629</v>
       </c>
       <c r="D19" t="n">
-        <v>6.670003720129873</v>
+        <v>7.22098998418431</v>
       </c>
       <c r="E19" t="n">
-        <v>21.41618803213641</v>
+        <v>20.45413418683679</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.99909358024961</v>
+        <v>2.297544882340641</v>
       </c>
       <c r="C20" t="n">
-        <v>14.92023836249245</v>
+        <v>12.87469829835493</v>
       </c>
       <c r="D20" t="n">
-        <v>7.056989030189881</v>
+        <v>7.774312807774855</v>
       </c>
       <c r="E20" t="n">
-        <v>23.97632097293194</v>
+        <v>22.94655598847042</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.189976392317559</v>
+        <v>1.383508317255733</v>
       </c>
       <c r="C21" t="n">
-        <v>10.96457069506416</v>
+        <v>9.503484674218846</v>
       </c>
       <c r="D21" t="n">
-        <v>5.861897732333196</v>
+        <v>6.51434762162154</v>
       </c>
       <c r="E21" t="n">
-        <v>18.01644481971492</v>
+        <v>17.40134061309612</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_93_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.251145592050259</v>
+        <v>1.273588344569341</v>
       </c>
       <c r="C3" t="n">
-        <v>4.598984248884189</v>
+        <v>4.626600811804652</v>
       </c>
       <c r="D3" t="n">
-        <v>6.076728767649644</v>
+        <v>6.08172586346426</v>
       </c>
       <c r="E3" t="n">
-        <v>11.92685860858409</v>
+        <v>11.98191501983825</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.37393670371728</v>
+        <v>1.425753703248446</v>
       </c>
       <c r="C4" t="n">
-        <v>5.047278060534623</v>
+        <v>5.113614305115434</v>
       </c>
       <c r="D4" t="n">
-        <v>6.264636678240109</v>
+        <v>6.300106109644426</v>
       </c>
       <c r="E4" t="n">
-        <v>12.68585144249201</v>
+        <v>12.83947411800831</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.542341257631959</v>
+        <v>1.638060726096795</v>
       </c>
       <c r="C5" t="n">
-        <v>5.594472545213489</v>
+        <v>5.714286548781002</v>
       </c>
       <c r="D5" t="n">
-        <v>6.567265043255849</v>
+        <v>6.690946972807083</v>
       </c>
       <c r="E5" t="n">
-        <v>13.7040788461013</v>
+        <v>14.04329424768488</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.747612221622471</v>
+        <v>1.8751682294458</v>
       </c>
       <c r="C6" t="n">
-        <v>6.242349971300674</v>
+        <v>6.3990993874914</v>
       </c>
       <c r="D6" t="n">
-        <v>6.948573607702313</v>
+        <v>7.056306914106408</v>
       </c>
       <c r="E6" t="n">
-        <v>14.93853580062546</v>
+        <v>15.33057453104361</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.982004758522603</v>
+        <v>2.132769728930121</v>
       </c>
       <c r="C7" t="n">
-        <v>6.998969857232018</v>
+        <v>7.160793083616031</v>
       </c>
       <c r="D7" t="n">
-        <v>7.371868606316609</v>
+        <v>7.393823453723902</v>
       </c>
       <c r="E7" t="n">
-        <v>16.35284322207123</v>
+        <v>16.68738626627005</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.226615879485393</v>
+        <v>1.323038855538845</v>
       </c>
       <c r="C8" t="n">
-        <v>4.641841978649753</v>
+        <v>4.689574808851711</v>
       </c>
       <c r="D8" t="n">
-        <v>5.616203594633136</v>
+        <v>5.579645006272252</v>
       </c>
       <c r="E8" t="n">
-        <v>11.48466145276828</v>
+        <v>11.59225867066281</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.557469885837648</v>
+        <v>1.65601077008096</v>
       </c>
       <c r="C9" t="n">
-        <v>5.659737826918178</v>
+        <v>5.601736113776476</v>
       </c>
       <c r="D9" t="n">
-        <v>6.110589224554074</v>
+        <v>6.002064433360164</v>
       </c>
       <c r="E9" t="n">
-        <v>13.3277969373099</v>
+        <v>13.2598113172176</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.911720116960858</v>
+        <v>2.022124106576047</v>
       </c>
       <c r="C10" t="n">
-        <v>6.824736639878211</v>
+        <v>6.659921237048104</v>
       </c>
       <c r="D10" t="n">
-        <v>6.660718469236911</v>
+        <v>6.465563303382323</v>
       </c>
       <c r="E10" t="n">
-        <v>15.39717522607598</v>
+        <v>15.14760864700648</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.285999411858154</v>
+        <v>2.411845713751096</v>
       </c>
       <c r="C11" t="n">
-        <v>8.10607334096418</v>
+        <v>7.901834620305446</v>
       </c>
       <c r="D11" t="n">
-        <v>7.303802725241177</v>
+        <v>7.019963990927987</v>
       </c>
       <c r="E11" t="n">
-        <v>17.69587547806351</v>
+        <v>17.33364432498453</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.661941224267887</v>
+        <v>2.814656214264824</v>
       </c>
       <c r="C12" t="n">
-        <v>9.471984570411204</v>
+        <v>9.234016946535919</v>
       </c>
       <c r="D12" t="n">
-        <v>7.830067568076478</v>
+        <v>7.503241562476616</v>
       </c>
       <c r="E12" t="n">
-        <v>19.96399336275557</v>
+        <v>19.55191472327736</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.029526068388456</v>
+        <v>3.208288284517279</v>
       </c>
       <c r="C13" t="n">
-        <v>10.87744797934758</v>
+        <v>10.64017039262555</v>
       </c>
       <c r="D13" t="n">
-        <v>8.426876708686668</v>
+        <v>7.970661333726555</v>
       </c>
       <c r="E13" t="n">
-        <v>22.33385075642271</v>
+        <v>21.81912001086939</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.745851759939145</v>
+        <v>1.863641849494678</v>
       </c>
       <c r="C14" t="n">
-        <v>7.648168045256182</v>
+        <v>7.613875597946841</v>
       </c>
       <c r="D14" t="n">
-        <v>6.450298401396479</v>
+        <v>6.055665276720388</v>
       </c>
       <c r="E14" t="n">
-        <v>15.84431820659181</v>
+        <v>15.53318272416191</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.798993763170025</v>
+        <v>1.923921158535432</v>
       </c>
       <c r="C15" t="n">
-        <v>8.198094021790034</v>
+        <v>8.183711417922817</v>
       </c>
       <c r="D15" t="n">
-        <v>6.528671320626502</v>
+        <v>6.063656703032957</v>
       </c>
       <c r="E15" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17128927949121</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.123490831854723</v>
+        <v>2.244540323788355</v>
       </c>
       <c r="C16" t="n">
-        <v>9.675084355444147</v>
+        <v>9.698410680897052</v>
       </c>
       <c r="D16" t="n">
-        <v>7.061721054124349</v>
+        <v>6.583011056056564</v>
       </c>
       <c r="E16" t="n">
-        <v>18.86029624142322</v>
+        <v>18.52596206074197</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.727944681813684</v>
+        <v>1.803048381188565</v>
       </c>
       <c r="C17" t="n">
-        <v>8.9639161359648</v>
+        <v>8.988518733433224</v>
       </c>
       <c r="D17" t="n">
-        <v>6.615114205985433</v>
+        <v>6.131348207240775</v>
       </c>
       <c r="E17" t="n">
-        <v>17.30697502376392</v>
+        <v>16.92291532186256</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.001940648591926</v>
+        <v>2.071850902611341</v>
       </c>
       <c r="C18" t="n">
-        <v>10.46276999099249</v>
+        <v>10.53857073123739</v>
       </c>
       <c r="D18" t="n">
-        <v>7.088277329524225</v>
+        <v>6.615595262360515</v>
       </c>
       <c r="E18" t="n">
-        <v>19.55298796910864</v>
+        <v>19.22601689620924</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.035752039526186</v>
+        <v>2.094126758020701</v>
       </c>
       <c r="C19" t="n">
-        <v>11.19739216312629</v>
+        <v>11.31735191510821</v>
       </c>
       <c r="D19" t="n">
-        <v>7.22098998418431</v>
+        <v>6.741956009374121</v>
       </c>
       <c r="E19" t="n">
-        <v>20.45413418683679</v>
+        <v>20.15343468250303</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.297544882340641</v>
+        <v>2.356881713585318</v>
       </c>
       <c r="C20" t="n">
-        <v>12.87469829835493</v>
+        <v>13.04663177379967</v>
       </c>
       <c r="D20" t="n">
-        <v>7.774312807774855</v>
+        <v>7.197094245062941</v>
       </c>
       <c r="E20" t="n">
-        <v>22.94655598847042</v>
+        <v>22.60060773244793</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.383508317255733</v>
+        <v>1.418487987958046</v>
       </c>
       <c r="C21" t="n">
-        <v>9.503484674218846</v>
+        <v>9.632613949758429</v>
       </c>
       <c r="D21" t="n">
-        <v>6.51434762162154</v>
+        <v>6.016326646211219</v>
       </c>
       <c r="E21" t="n">
-        <v>17.40134061309612</v>
+        <v>17.06742858392769</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_93_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_93_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.273588344569341</v>
+        <v>2.598724964933007</v>
       </c>
       <c r="C3" t="n">
-        <v>4.626600811804652</v>
+        <v>7.695642533590064</v>
       </c>
       <c r="D3" t="n">
-        <v>6.08172586346426</v>
+        <v>8.236379987313081</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98191501983825</v>
+        <v>18.53074748583615</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.425753703248446</v>
+        <v>1.099976132018086</v>
       </c>
       <c r="C4" t="n">
-        <v>5.113614305115434</v>
+        <v>4.522098756801955</v>
       </c>
       <c r="D4" t="n">
-        <v>6.300106109644426</v>
+        <v>5.839710004333806</v>
       </c>
       <c r="E4" t="n">
-        <v>12.83947411800831</v>
+        <v>11.46178489315385</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.638060726096795</v>
+        <v>1.223474955928914</v>
       </c>
       <c r="C5" t="n">
-        <v>5.714286548781002</v>
+        <v>5.221621792752881</v>
       </c>
       <c r="D5" t="n">
-        <v>6.690946972807083</v>
+        <v>6.131760120477021</v>
       </c>
       <c r="E5" t="n">
-        <v>14.04329424768488</v>
+        <v>12.57685686915882</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.8751682294458</v>
+        <v>1.355580755836273</v>
       </c>
       <c r="C6" t="n">
-        <v>6.3990993874914</v>
+        <v>6.122345650071439</v>
       </c>
       <c r="D6" t="n">
-        <v>7.056306914106408</v>
+        <v>6.425709420691837</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33057453104361</v>
+        <v>13.90363582659955</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.132769728930121</v>
+        <v>1.490904642879964</v>
       </c>
       <c r="C7" t="n">
-        <v>7.160793083616031</v>
+        <v>7.173338889685055</v>
       </c>
       <c r="D7" t="n">
-        <v>7.393823453723902</v>
+        <v>6.767165326716099</v>
       </c>
       <c r="E7" t="n">
-        <v>16.68738626627005</v>
+        <v>15.43140885928112</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.323038855538845</v>
+        <v>1.639771245101112</v>
       </c>
       <c r="C8" t="n">
-        <v>4.689574808851711</v>
+        <v>8.412539150181257</v>
       </c>
       <c r="D8" t="n">
-        <v>5.579645006272252</v>
+        <v>7.137030251668581</v>
       </c>
       <c r="E8" t="n">
-        <v>11.59225867066281</v>
+        <v>17.18934064695095</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.65601077008096</v>
+        <v>1.788421379631267</v>
       </c>
       <c r="C9" t="n">
-        <v>5.601736113776476</v>
+        <v>9.826618705607467</v>
       </c>
       <c r="D9" t="n">
-        <v>6.002064433360164</v>
+        <v>7.536343366522447</v>
       </c>
       <c r="E9" t="n">
-        <v>13.2598113172176</v>
+        <v>19.15138345176118</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.022124106576047</v>
+        <v>1.110818074924139</v>
       </c>
       <c r="C10" t="n">
-        <v>6.659921237048104</v>
+        <v>7.228490536644755</v>
       </c>
       <c r="D10" t="n">
-        <v>6.465563303382323</v>
+        <v>5.90877618521098</v>
       </c>
       <c r="E10" t="n">
-        <v>15.14760864700648</v>
+        <v>14.24808479677987</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.411845713751096</v>
+        <v>1.060788211915721</v>
       </c>
       <c r="C11" t="n">
-        <v>7.901834620305446</v>
+        <v>7.84812060018013</v>
       </c>
       <c r="D11" t="n">
-        <v>7.019963990927987</v>
+        <v>5.737628107929633</v>
       </c>
       <c r="E11" t="n">
-        <v>17.33364432498453</v>
+        <v>14.64653692002548</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.814656214264824</v>
+        <v>1.156822772345144</v>
       </c>
       <c r="C12" t="n">
-        <v>9.234016946535919</v>
+        <v>9.423806030542176</v>
       </c>
       <c r="D12" t="n">
-        <v>7.503241562476616</v>
+        <v>6.167800499499459</v>
       </c>
       <c r="E12" t="n">
-        <v>19.55191472327736</v>
+        <v>16.74842930238678</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.208288284517279</v>
+        <v>0.9150477652202822</v>
       </c>
       <c r="C13" t="n">
-        <v>10.64017039262555</v>
+        <v>9.08006670685424</v>
       </c>
       <c r="D13" t="n">
-        <v>7.970661333726555</v>
+        <v>5.622488737175567</v>
       </c>
       <c r="E13" t="n">
-        <v>21.81912001086939</v>
+        <v>15.61760320925009</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.863641849494678</v>
+        <v>0.9901907345033331</v>
       </c>
       <c r="C14" t="n">
-        <v>7.613875597946841</v>
+        <v>10.70995442796775</v>
       </c>
       <c r="D14" t="n">
-        <v>6.055665276720388</v>
+        <v>5.948919848837633</v>
       </c>
       <c r="E14" t="n">
-        <v>15.53318272416191</v>
+        <v>17.64906501130872</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.923921158535432</v>
+        <v>0.957979592326995</v>
       </c>
       <c r="C15" t="n">
-        <v>8.183711417922817</v>
+        <v>11.62926297822447</v>
       </c>
       <c r="D15" t="n">
-        <v>6.063656703032957</v>
+        <v>5.982662517432596</v>
       </c>
       <c r="E15" t="n">
-        <v>16.17128927949121</v>
+        <v>18.56990508798406</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.244540323788355</v>
+        <v>1.046160171122444</v>
       </c>
       <c r="C16" t="n">
-        <v>9.698410680897052</v>
+        <v>13.59504585886898</v>
       </c>
       <c r="D16" t="n">
-        <v>6.583011056056564</v>
+        <v>6.383745724525587</v>
       </c>
       <c r="E16" t="n">
-        <v>18.52596206074197</v>
+        <v>21.02495175451701</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.803048381188565</v>
+        <v>0.6238024912784234</v>
       </c>
       <c r="C17" t="n">
-        <v>8.988518733433224</v>
+        <v>10.18314860986891</v>
       </c>
       <c r="D17" t="n">
-        <v>6.131348207240775</v>
+        <v>5.291541586073969</v>
       </c>
       <c r="E17" t="n">
-        <v>16.92291532186256</v>
+        <v>16.09849268722131</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.071850902611341</v>
+        <v>0.4929060698711962</v>
       </c>
       <c r="C18" t="n">
-        <v>10.53857073123739</v>
+        <v>9.192781160778818</v>
       </c>
       <c r="D18" t="n">
-        <v>6.615595262360515</v>
+        <v>4.817347627445717</v>
       </c>
       <c r="E18" t="n">
-        <v>19.22601689620924</v>
+        <v>14.50303485809573</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.094126758020701</v>
+        <v>0.5733013893719674</v>
       </c>
       <c r="C19" t="n">
-        <v>11.31735191510821</v>
+        <v>11.4361728397532</v>
       </c>
       <c r="D19" t="n">
-        <v>6.741956009374121</v>
+        <v>5.247677098648221</v>
       </c>
       <c r="E19" t="n">
-        <v>20.15343468250303</v>
+        <v>17.25715132777339</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.356881713585318</v>
+        <v>0.6498777103032186</v>
       </c>
       <c r="C20" t="n">
-        <v>13.04663177379967</v>
+        <v>13.7906689064172</v>
       </c>
       <c r="D20" t="n">
-        <v>7.197094245062941</v>
+        <v>5.655122030864733</v>
       </c>
       <c r="E20" t="n">
-        <v>22.60060773244793</v>
+        <v>20.09566864758515</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.418487987958046</v>
+        <v>0.7189043913888119</v>
       </c>
       <c r="C21" t="n">
-        <v>9.632613949758429</v>
+        <v>16.25323576036469</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016326646211219</v>
+        <v>6.031848077415361</v>
       </c>
       <c r="E21" t="n">
-        <v>17.06742858392769</v>
+        <v>23.00398822916886</v>
       </c>
     </row>
   </sheetData>
